--- a/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0002T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0002T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.7415101541919</v>
+        <v>7.920495400056184</v>
       </c>
       <c r="D2" t="n">
-        <v>49.14116299167148</v>
+        <v>7.985438986146615</v>
       </c>
       <c r="E2" t="n">
-        <v>4.256133448154035</v>
+        <v>0.691621685325031</v>
       </c>
       <c r="F2" t="n">
-        <v>4.279767876472871</v>
+        <v>0.6954622799268413</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.22924325788383</v>
+        <v>6.537252029406122</v>
       </c>
       <c r="D3" t="n">
-        <v>40.58162723872574</v>
+        <v>6.594514426292933</v>
       </c>
       <c r="E3" t="n">
-        <v>4.256133448154035</v>
+        <v>0.691621685325031</v>
       </c>
       <c r="F3" t="n">
-        <v>4.279767876472871</v>
+        <v>0.6954622799268413</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
